--- a/merge/StructureDefinition-bc-add-response-bundle.xlsx
+++ b/merge/StructureDefinition-bc-add-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T00:47:30+00:00</t>
+    <t>2026-03-25T21:32:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
